--- a/docs/qa/upload-templates/lead_time_upload_template.xlsx
+++ b/docs/qa/upload-templates/lead_time_upload_template.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,21 @@
           <t>lead_time_days</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>min_qty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>incoterm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,6 +478,19 @@
       <c r="C2" t="n">
         <v>12</v>
       </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EXW</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,11 +506,24 @@
       <c r="C3" t="n">
         <v>10</v>
       </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RM-CORE</t>
+          <t>SF-CORE100</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -492,6 +533,19 @@
       </c>
       <c r="C4" t="n">
         <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FCA</t>
+        </is>
       </c>
     </row>
   </sheetData>
